--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-23T01:54:32+00:00</t>
+    <t>2024-10-27T05:37:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18T09:56:39+00:00</t>
+    <t>2024-11-18T12:36:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18T12:36:42+00:00</t>
+    <t>2024-11-18T13:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
